--- a/artfynd/A 42074-2026 artfynd.xlsx
+++ b/artfynd/A 42074-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137153360</v>
       </c>
       <c r="B2" t="n">
-        <v>98256</v>
+        <v>98266</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42074-2026 artfynd.xlsx
+++ b/artfynd/A 42074-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137153360</v>
       </c>
       <c r="B2" t="n">
-        <v>98266</v>
+        <v>98267</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42074-2026 artfynd.xlsx
+++ b/artfynd/A 42074-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137153360</v>
       </c>
       <c r="B2" t="n">
-        <v>98267</v>
+        <v>98272</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42074-2026 artfynd.xlsx
+++ b/artfynd/A 42074-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137153360</v>
       </c>
       <c r="B2" t="n">
-        <v>98272</v>
+        <v>98274</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42074-2026 artfynd.xlsx
+++ b/artfynd/A 42074-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137153360</v>
       </c>
       <c r="B2" t="n">
-        <v>98274</v>
+        <v>98280</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42074-2026 artfynd.xlsx
+++ b/artfynd/A 42074-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137153360</v>
       </c>
       <c r="B2" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42074-2026 artfynd.xlsx
+++ b/artfynd/A 42074-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137153360</v>
       </c>
       <c r="B2" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42074-2026 artfynd.xlsx
+++ b/artfynd/A 42074-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137153360</v>
       </c>
       <c r="B2" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42074-2026 artfynd.xlsx
+++ b/artfynd/A 42074-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137153360</v>
       </c>
       <c r="B2" t="n">
-        <v>98296</v>
+        <v>98300</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
